--- a/app/ByCoach.xlsx
+++ b/app/ByCoach.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pooh\PythonPooh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rditlhm9\Documents\FileCloud\My Files\Documents\Personal\Pooh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181BA171-E8D3-4C63-A2E0-DBE6E6C91DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53365107-5D06-4C84-B3F3-4FEEA2F65388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{752F0373-71A3-4143-AEE7-1FF2B10D43F8}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{752F0373-71A3-4143-AEE7-1FF2B10D43F8}"/>
   </bookViews>
   <sheets>
     <sheet name="by Coach" sheetId="1" r:id="rId1"/>
@@ -485,9 +485,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -525,7 +525,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -631,7 +631,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -773,7 +773,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -782,15 +782,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E2BC0AC-145D-487F-B54D-229B32AB9043}">
   <dimension ref="A1:C85"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="24.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="24.7890625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5234375" style="6" customWidth="1"/>
     <col min="3" max="3" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="2"/>
+    <col min="4" max="16384" width="8.89453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -801,7 +801,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -812,7 +812,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -823,7 +823,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -834,7 +834,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -845,7 +845,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -856,7 +856,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -867,7 +867,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -878,7 +878,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -889,7 +889,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="4" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" s="4" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
@@ -900,7 +900,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
@@ -911,7 +911,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -922,7 +922,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
@@ -933,7 +933,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="5" t="s">
         <v>15</v>
       </c>
@@ -944,7 +944,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
@@ -955,7 +955,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A16" s="5" t="s">
         <v>18</v>
       </c>
@@ -966,7 +966,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
@@ -977,7 +977,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
@@ -988,7 +988,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" s="5" t="s">
         <v>21</v>
       </c>
@@ -999,7 +999,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A20" s="5" t="s">
         <v>22</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A21" s="5" t="s">
         <v>23</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22" s="5" t="s">
         <v>24</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="5" t="s">
         <v>25</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A25" s="5" t="s">
         <v>27</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A30" s="3" t="s">
         <v>33</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A31" s="3" t="s">
         <v>34</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A32" s="3" t="s">
         <v>35</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A33" s="3" t="s">
         <v>36</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A34" s="3" t="s">
         <v>37</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A35" s="3" t="s">
         <v>38</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A36" s="3" t="s">
         <v>39</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A37" s="3" t="s">
         <v>40</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38" s="5" t="s">
         <v>41</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A39" s="5" t="s">
         <v>43</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A40" s="5" t="s">
         <v>44</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A41" s="5" t="s">
         <v>45</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A42" s="5" t="s">
         <v>46</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A43" s="5" t="s">
         <v>47</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A44" s="5" t="s">
         <v>48</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A45" s="5" t="s">
         <v>49</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A46" s="5" t="s">
         <v>50</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A47" s="5" t="s">
         <v>51</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A48" s="5" t="s">
         <v>52</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A49" s="5" t="s">
         <v>53</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A50" s="3" t="s">
         <v>54</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A51" s="3" t="s">
         <v>56</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A52" s="3" t="s">
         <v>57</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A53" s="3" t="s">
         <v>58</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A54" s="3" t="s">
         <v>59</v>
       </c>
@@ -1384,7 +1384,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A55" s="3" t="s">
         <v>60</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A56" s="3" t="s">
         <v>61</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A57" s="3" t="s">
         <v>62</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A58" s="3" t="s">
         <v>63</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A59" s="3" t="s">
         <v>64</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A60" s="3" t="s">
         <v>65</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A61" s="3" t="s">
         <v>66</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A62" s="5" t="s">
         <v>67</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A63" s="5" t="s">
         <v>69</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A64" s="5" t="s">
         <v>70</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A65" s="5" t="s">
         <v>71</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A66" s="5" t="s">
         <v>72</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A67" s="5" t="s">
         <v>73</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A68" s="5" t="s">
         <v>74</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A69" s="5" t="s">
         <v>75</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A70" s="5" t="s">
         <v>76</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A71" s="5" t="s">
         <v>77</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A72" s="5" t="s">
         <v>78</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A73" s="5" t="s">
         <v>79</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A74" s="3" t="s">
         <v>80</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A75" s="3" t="s">
         <v>82</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A76" s="3" t="s">
         <v>83</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A77" s="3" t="s">
         <v>84</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A78" s="3" t="s">
         <v>85</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A79" s="3" t="s">
         <v>86</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A80" s="3" t="s">
         <v>87</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A81" s="3" t="s">
         <v>88</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A82" s="3" t="s">
         <v>89</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A83" s="3" t="s">
         <v>90</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A84" s="3" t="s">
         <v>91</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A85" s="3" t="s">
         <v>92</v>
       </c>

--- a/app/ByCoach.xlsx
+++ b/app/ByCoach.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rditlhm9\Documents\FileCloud\My Files\Documents\Personal\Pooh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53365107-5D06-4C84-B3F3-4FEEA2F65388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6319233F-7E18-4DD6-B2A1-8E08B92AB7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{752F0373-71A3-4143-AEE7-1FF2B10D43F8}"/>
   </bookViews>
@@ -842,7 +842,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
@@ -875,7 +875,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
@@ -1282,7 +1282,7 @@
         <v>42</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
@@ -1293,7 +1293,7 @@
         <v>42</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
@@ -1381,7 +1381,7 @@
         <v>55</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
@@ -1414,7 +1414,7 @@
         <v>55</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
@@ -1700,7 +1700,7 @@
         <v>81</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
@@ -1711,7 +1711,7 @@
         <v>81</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.5">
